--- a/data/trans_orig/IP04D$colectiva-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP04D$colectiva-Edad-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4185</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13406</t>
+          <t>13885</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1447</t>
+          <t>1562</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8814</t>
+          <t>9361</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7485</t>
+          <t>7629</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18723</t>
+          <t>18805</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>131047</t>
+          <t>130568</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>140017</t>
+          <t>140268</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>136548</t>
+          <t>136001</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>143915</t>
+          <t>143800</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>271091</t>
+          <t>271009</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>282329</t>
+          <t>282185</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2675</t>
+          <t>2616</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11494</t>
+          <t>10737</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4796</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16412</t>
+          <t>15897</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9260</t>
+          <t>9595</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23127</t>
+          <t>23568</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>224756</t>
+          <t>225513</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>233575</t>
+          <t>233634</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>251925</t>
+          <t>252440</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>263541</t>
+          <t>263078</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>481460</t>
+          <t>481019</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>495327</t>
+          <t>494992</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2196</t>
+          <t>2181</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10181</t>
+          <t>9513</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2097</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9762</t>
+          <t>9477</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5694</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15749</t>
+          <t>15682</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>146072</t>
+          <t>146740</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>154057</t>
+          <t>154072</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>148809</t>
+          <t>149094</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>156556</t>
+          <t>156474</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>299075</t>
+          <t>299142</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>309746</t>
+          <t>309130</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2726</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11538</t>
+          <t>10937</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>638</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6396</t>
+          <t>6421</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4602</t>
+          <t>4655</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>14364</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>159799</t>
+          <t>160400</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>168611</t>
+          <t>168665</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>173559</t>
+          <t>173534</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>179323</t>
+          <t>179317</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>337188</t>
+          <t>336928</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>346690</t>
+          <t>346637</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17982</t>
+          <t>17440</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34398</t>
+          <t>32935</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15008</t>
+          <t>14277</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30035</t>
+          <t>29047</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35902</t>
+          <t>34629</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57350</t>
+          <t>58113</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>673894</t>
+          <t>675357</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>690310</t>
+          <t>690852</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>722190</t>
+          <t>723178</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>737217</t>
+          <t>737948</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1403167</t>
+          <t>1402404</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1424615</t>
+          <t>1425888</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>2464</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9583</t>
+          <t>9994</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>666</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5106</t>
+          <t>5720</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3544</t>
+          <t>3931</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12287</t>
+          <t>12191</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>122071</t>
+          <t>121660</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>129542</t>
+          <t>129190</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>119058</t>
+          <t>118444</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>123496</t>
+          <t>123498</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>243531</t>
+          <t>243627</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>252274</t>
+          <t>251887</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,46%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3840</t>
+          <t>3953</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12703</t>
+          <t>12714</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>4402</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14073</t>
+          <t>14398</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10280</t>
+          <t>9980</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22476</t>
+          <t>23236</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>195745</t>
+          <t>195734</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>204608</t>
+          <t>204495</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>242011</t>
+          <t>241686</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>251781</t>
+          <t>251682</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>442056</t>
+          <t>441296</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>454252</t>
+          <t>454552</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,85%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3451</t>
+          <t>2840</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12040</t>
+          <t>11394</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2155</t>
+          <t>2126</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10278</t>
+          <t>10008</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7096</t>
+          <t>7158</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18624</t>
+          <t>18198</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>175400</t>
+          <t>176046</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>183989</t>
+          <t>184600</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>176109</t>
+          <t>176379</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>184232</t>
+          <t>184261</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>355203</t>
+          <t>355629</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>366731</t>
+          <t>366669</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,09%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2241</t>
+          <t>2231</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10384</t>
+          <t>10517</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6034</t>
+          <t>5978</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17223</t>
+          <t>17402</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>9893</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23380</t>
+          <t>24023</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>162254</t>
+          <t>162121</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>170397</t>
+          <t>170407</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>156154</t>
+          <t>155975</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>167343</t>
+          <t>167399</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>322635</t>
+          <t>321992</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>336377</t>
+          <t>336122</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,14%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17392</t>
+          <t>18023</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33867</t>
+          <t>34452</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19382</t>
+          <t>18514</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35710</t>
+          <t>35369</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40111</t>
+          <t>40100</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>64109</t>
+          <t>63666</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>666314</t>
+          <t>665729</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>682789</t>
+          <t>682158</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>704301</t>
+          <t>704642</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>720629</t>
+          <t>721497</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1376083</t>
+          <t>1376526</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1400081</t>
+          <t>1400092</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,22%</t>
         </is>
       </c>
     </row>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>1745</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6883</t>
+          <t>7188</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8041</t>
+          <t>7799</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5110</t>
+          <t>5443</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12326</t>
+          <t>13185</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>11,08%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50628</t>
+          <t>50323</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55545</t>
+          <t>55766</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53403</t>
+          <t>53645</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58954</t>
+          <t>59109</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>106629</t>
+          <t>105770</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>113845</t>
+          <t>113512</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,42%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7941</t>
+          <t>8392</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18320</t>
+          <t>18739</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6565</t>
+          <t>6186</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16805</t>
+          <t>16149</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16478</t>
+          <t>16839</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31584</t>
+          <t>32493</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>140979</t>
+          <t>140560</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>151358</t>
+          <t>150907</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>165042</t>
+          <t>165698</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>175282</t>
+          <t>175661</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>309563</t>
+          <t>308654</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>324669</t>
+          <t>324308</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,06%</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8741</t>
+          <t>9055</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21294</t>
+          <t>22012</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11869</t>
+          <t>11103</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26099</t>
+          <t>26316</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23998</t>
+          <t>23469</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43017</t>
+          <t>42485</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,02%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>152594</t>
+          <t>151876</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>165147</t>
+          <t>164833</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>185448</t>
+          <t>185231</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>199678</t>
+          <t>200444</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>342417</t>
+          <t>342949</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>361436</t>
+          <t>361965</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,91%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13513</t>
+          <t>14110</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30471</t>
+          <t>29617</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13709</t>
+          <t>12981</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28988</t>
+          <t>28886</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30462</t>
+          <t>29969</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53130</t>
+          <t>52412</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>243987</t>
+          <t>244841</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>260945</t>
+          <t>260348</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>276495</t>
+          <t>276597</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>291774</t>
+          <t>292502</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>526811</t>
+          <t>527529</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>549479</t>
+          <t>549972</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,83%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>41484</t>
+          <t>41031</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>64809</t>
+          <t>64200</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>42303</t>
+          <t>41076</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>65963</t>
+          <t>65804</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>87935</t>
+          <t>89985</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>122650</t>
+          <t>122939</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>600347</t>
+          <t>600956</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>623672</t>
+          <t>624125</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>694359</t>
+          <t>694518</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>718019</t>
+          <t>719246</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1302827</t>
+          <t>1302538</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1337542</t>
+          <t>1335492</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,69%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP04D$colectiva-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP04D$colectiva-Edad-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4316</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1490</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8871</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,97%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6,1%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>8155</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4185</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>13885</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4565</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>14321</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>5,65%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,61%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4316</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1562</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>9361</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7629</t>
+          <t>7507</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18805</t>
+          <t>19333</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>141046</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>136491</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>143872</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,03%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>93,9%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,98%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>204</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>136298</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>130568</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>140268</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>130132</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>139888</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>94,35%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>90,39%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,1%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>141046</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>136001</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>143800</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,03%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>271009</t>
+          <t>270481</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>282185</t>
+          <t>282307</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,41%</t>
         </is>
       </c>
     </row>
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>145362</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>145362</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>145362</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>144453</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>144453</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>144453</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>145362</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>145362</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>145362</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>9284</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5018</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>15860</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,46%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5,91%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>5748</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2616</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>10737</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2542</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>11000</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,43%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,54%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>9284</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>5259</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>15897</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,46%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9595</t>
+          <t>8667</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23568</t>
+          <t>22133</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>259053</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>252477</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>263319</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,54%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>94,09%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,13%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>230502</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>225513</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>233634</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>225250</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>233708</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,57%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>95,46%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,89%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>361</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>259053</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>252440</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>263078</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,54%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>481019</t>
+          <t>482454</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>494992</t>
+          <t>495920</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>373</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>268337</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>268337</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>268337</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>340</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>373</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>268337</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>268337</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>268337</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1413,67 +1413,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>4805</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2082</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9190</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,03%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,8%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>5100</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2181</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9513</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2290</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>10078</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,26%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,09%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4805</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2097</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9477</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,03%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5694</t>
+          <t>5577</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15682</t>
+          <t>15944</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>153766</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>149381</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>156489</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,97%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>94,2%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,69%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>151153</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>146740</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>154072</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>146175</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>153963</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>96,74%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>93,91%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,6%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>153766</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>149094</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>156474</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,97%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>299142</t>
+          <t>298880</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>309130</t>
+          <t>309247</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>156253</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>156253</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>156253</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2567</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6401</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,56%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>5799</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2672</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>10937</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2558</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>10980</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,38%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,38%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2567</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>638</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6421</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4655</t>
+          <t>4625</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14364</t>
+          <t>14579</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>177388</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>173554</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>179308</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,57%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96,44%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,64%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>165538</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>160400</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>168665</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>160357</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>168779</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>96,62%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>93,62%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,44%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>177388</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>173534</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>179317</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,57%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>336928</t>
+          <t>336713</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>346637</t>
+          <t>346667</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,107 +2094,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>20972</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>14210</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>29957</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,79%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,98%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>24802</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>17440</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>32935</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>18213</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>33912</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>3,5%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>4,79%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>45774</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>35876</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>58667</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>3,13%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>2,46%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,65%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>20972</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>14277</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>29047</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>3,86%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>45774</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>34629</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>58113</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>3,13%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -2207,107 +2207,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1043</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>731253</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>722268</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>738015</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,21%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96,02%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,11%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>986</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>683490</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>675357</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>690852</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>674380</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>690079</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>96,5%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>95,35%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>95,21%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>97,43%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>1414743</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>1401850</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>1424641</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>96,87%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>95,98%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
         <is>
           <t>97,54%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1043</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>731253</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>723178</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>737948</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>97,21%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>96,14%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>98,1%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1414743</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>1402404</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1425888</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>96,87%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>96,02%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1072</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>752225</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>752225</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>752225</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1021</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>708292</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>708292</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>708292</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1072</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>752225</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>752225</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>752225</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2124</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5754</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4,63%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>5322</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2464</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9994</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2599</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>10560</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>4,04%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,59%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2124</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>666</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5720</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12191</t>
+          <t>13479</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>122040</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>118410</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>123497</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,29%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>95,37%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,46%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>126332</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>121660</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>129190</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>121094</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>129055</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>95,96%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>92,41%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,13%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>122040</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>118444</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>123498</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,29%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>243627</t>
+          <t>242339</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>251887</t>
+          <t>251852</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8428</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4598</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>14446</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,29%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5,64%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>7274</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3953</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>12714</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3837</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>12744</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>3,49%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,1%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>8428</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>4402</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>14398</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,29%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9980</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23236</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>247656</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>241638</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>251486</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,71%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>94,36%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,2%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>318</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>201174</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>195734</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>204495</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>195704</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>204611</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>96,51%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>93,9%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,1%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>363</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>247656</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>241686</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>251682</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,71%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>441296</t>
+          <t>441062</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>454552</t>
+          <t>454140</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,76%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>256084</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>256084</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>256084</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>329</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>208448</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>208448</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>208448</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>256084</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>256084</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>256084</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5115</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2111</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9639</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,17%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>6460</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2840</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11394</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3345</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>12042</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,45%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,08%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5115</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2126</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>10008</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,74%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7158</t>
+          <t>6939</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18198</t>
+          <t>18393</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>181272</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>176748</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>184276</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,26%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>94,83%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,87%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>261</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>180980</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>176046</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>184600</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>175398</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>184095</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>96,55%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>93,92%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,48%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>181272</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>176379</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>184261</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,26%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>355629</t>
+          <t>355434</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>366669</t>
+          <t>366888</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,14%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>186387</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>186387</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>186387</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>187440</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>187440</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>187440</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>186387</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>186387</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>186387</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,72 +3698,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10541</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5957</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>16807</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6,08%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9,69%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>5220</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2231</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>10517</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2235</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>11036</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,02%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>1,29%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,09%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>10541</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>5978</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>17402</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>6,08%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>3,45%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9893</t>
+          <t>9876</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24023</t>
+          <t>23186</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -3811,74 +3811,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>162836</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>156570</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>167420</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>93,92%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>90,31%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96,56%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>238</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>167418</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>162121</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>170407</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>161602</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>170403</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>96,98%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>93,91%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>93,61%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>98,71%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>162836</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>155975</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>167399</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>93,92%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>89,96%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>96,55%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>458</t>
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>321992</t>
+          <t>322829</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>336122</t>
+          <t>336139</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,15%</t>
         </is>
       </c>
     </row>
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>173377</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>173377</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>173377</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>172638</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>172638</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>172638</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>173377</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>173377</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>173377</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>26208</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>19093</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>35833</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,54%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,84%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>24276</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>18023</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>34452</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>17194</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>32882</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>3,47%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,57%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,92%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>26208</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>18514</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>35369</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40100</t>
+          <t>38814</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>63666</t>
+          <t>62323</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -4159,67 +4159,67 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>713803</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>704178</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>720918</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>96,46%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>95,16%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>97,42%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
           <t>675905</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>665729</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>682158</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>667299</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>682987</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>96,53%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>95,08%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97,43%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1020</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>713803</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>704642</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>721497</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>96,46%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1376526</t>
+          <t>1377869</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1400092</t>
+          <t>1401378</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,3%</t>
         </is>
       </c>
     </row>
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1058</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>740011</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>740011</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>740011</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1055</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>700181</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>700181</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>700181</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1058</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>740011</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>740011</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>740011</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4616,72 +4616,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3244</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1714</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5761</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6,42%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,39%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>11,4%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3819</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1745</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7188</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6,64%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,03%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12,5%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4522</t>
+          <t>3308</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2335</t>
+          <t>1545</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7799</t>
+          <t>6107</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4691,32 +4691,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>8341</t>
+          <t>6552</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5443</t>
+          <t>4086</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13185</t>
+          <t>9712</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -4729,72 +4729,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>47293</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>44776</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>48823</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>93,58%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>88,6%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>96,61%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>53692</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>50323</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>55766</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>93,36%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>87,5%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>96,97%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>56922</t>
+          <t>48782</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53645</t>
+          <t>45983</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59109</t>
+          <t>50545</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4804,32 +4804,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>110614</t>
+          <t>96075</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>105770</t>
+          <t>92915</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>113512</t>
+          <t>98541</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4959,72 +4959,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8516</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5002</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>13966</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,43%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,9%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>12719</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>8392</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>18739</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>7,98%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5,27%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>11,76%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10682</t>
+          <t>12204</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6186</t>
+          <t>7897</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16149</t>
+          <t>18474</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5034,32 +5034,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>23401</t>
+          <t>20720</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16839</t>
+          <t>14537</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32493</t>
+          <t>29653</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -5072,72 +5072,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>148389</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>142939</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>151903</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94,57%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>91,1%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,81%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>237</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>146580</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>140560</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>150907</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>92,02%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>88,24%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>94,73%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>171165</t>
+          <t>133314</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>165698</t>
+          <t>127044</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>175661</t>
+          <t>137621</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5147,32 +5147,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>317746</t>
+          <t>281703</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>308654</t>
+          <t>272770</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>324308</t>
+          <t>287886</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,19%</t>
         </is>
       </c>
     </row>
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>156905</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>156905</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>156905</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>181847</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181847</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181847</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5260,17 +5260,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341147</t>
+          <t>302423</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341147</t>
+          <t>302423</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341147</t>
+          <t>302423</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5302,72 +5302,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>16823</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10962</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>24764</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8,45%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5,5%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>12,43%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>14085</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>9055</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>22012</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8,1%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,21%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12,66%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>17916</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11103</t>
+          <t>9448</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26316</t>
+          <t>22533</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5377,32 +5377,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>32001</t>
+          <t>31226</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23469</t>
+          <t>22557</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42485</t>
+          <t>41624</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,11%</t>
         </is>
       </c>
     </row>
@@ -5415,72 +5415,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>182346</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>174405</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>188207</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>91,55%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>87,57%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>94,5%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>214</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>159803</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>151876</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>164833</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>91,9%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>87,34%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>94,79%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>193631</t>
+          <t>161115</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>185231</t>
+          <t>152985</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>200444</t>
+          <t>166070</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5490,32 +5490,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>353433</t>
+          <t>343460</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>342949</t>
+          <t>333062</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>361965</t>
+          <t>352129</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,98%</t>
         </is>
       </c>
     </row>
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>199169</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>199169</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>199169</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>211547</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>211547</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>211547</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5603,17 +5603,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385434</t>
+          <t>374686</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385434</t>
+          <t>374686</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385434</t>
+          <t>374686</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>18968</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>12705</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>27465</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6,48%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4,34%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9,39%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>21501</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>14110</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>29617</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>7,83%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5,14%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10,79%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19643</t>
+          <t>23009</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12981</t>
+          <t>15644</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28886</t>
+          <t>31207</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>41144</t>
+          <t>41977</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29969</t>
+          <t>32526</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>52412</t>
+          <t>54351</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -5758,72 +5758,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>273677</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>265180</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>279940</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>93,52%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>90,61%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>95,66%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>309</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>252957</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>244841</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>260348</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>92,17%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>89,21%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>94,86%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>314</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>285840</t>
+          <t>232469</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>276597</t>
+          <t>224271</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>292502</t>
+          <t>239834</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>538797</t>
+          <t>506145</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>527529</t>
+          <t>493771</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>549972</t>
+          <t>515596</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,07%</t>
         </is>
       </c>
     </row>
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>292645</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>292645</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>292645</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>274458</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>274458</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>274458</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>255478</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>255478</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>255478</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5946,17 +5946,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>579941</t>
+          <t>548122</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>579941</t>
+          <t>548122</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>579941</t>
+          <t>548122</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>47551</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>37489</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>59236</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,8%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5,36%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8,47%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>52125</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>41031</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>64200</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>7,84%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>6,17%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>9,65%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>52763</t>
+          <t>52924</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>41076</t>
+          <t>42864</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>65804</t>
+          <t>66630</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>104888</t>
+          <t>100475</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>89985</t>
+          <t>85194</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>122939</t>
+          <t>115246</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,68%</t>
         </is>
       </c>
     </row>
@@ -6101,72 +6101,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>651705</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>640020</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>661767</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>93,2%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>91,53%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>94,64%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>860</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>613031</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>600956</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>624125</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>92,16%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>90,35%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>93,83%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>897</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>707559</t>
+          <t>575679</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>694518</t>
+          <t>561973</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>719246</t>
+          <t>585739</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6176,32 +6176,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1320589</t>
+          <t>1227384</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1302538</t>
+          <t>1212613</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1335492</t>
+          <t>1242665</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,58%</t>
         </is>
       </c>
     </row>
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>975</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>699256</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>699256</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>699256</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>665156</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>665156</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>665156</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>760322</t>
+          <t>628603</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>760322</t>
+          <t>628603</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>760322</t>
+          <t>628603</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6289,17 +6289,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1425477</t>
+          <t>1327859</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1425477</t>
+          <t>1327859</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1425477</t>
+          <t>1327859</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
